--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_8/224FL_10A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_8/224FL_10A.xlsx
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -7675,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
